--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>68/100</t>
+          <t>64/100</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Extraction / vraie restauration possible</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Situé dans le secteur de la rue Henri Barbusse à Saint-Denis, ce local commercial s’inscrit dans un environnement urbain et commerçant, bénéficiant d’un flux piéton et automobile régulier et de la proximité immédiate des commerces de quartier et services ; il est facilement accessible grâce aux transports en commun à proximité (métro, RER et lignes de bus desservant le centre de Saint-Denis), ainsi qu’aux axes routiers principaux reliant rapidement Paris et la proche banlieue ; le local développe une surface totale de 108 m², comprenant 57 m² en rez-de-chaussée et 51 m² de réserve en sous-sol</t>
+          <t>Situé dans le secteur de la rue Henri Barbusse à Saint-Denis, ce local commercial s’inscrit dans un environnement urbain et commerçant, bénéficiant d’un flux piéton et automobile régulier et de la proximité immédiate des commerces de quartier et services ; il est facilement accessible grâce aux transports en commun à proximité (métro, RER et lignes de bus desservant le centre de Saint-Denis), ainsi qu’aux axes routiers principaux reliant rapidement Paris et la proche banlieue ; le local développe une surface totale de 108 m², comprenant 57 m² en rez-de-chaussée et 51 m² de réserve en sous-sol ; il est occupé par le même locataire depuis 20 ans, avec un loyer annuel de 14 100 €, des charges de 800 € par an et une taxe foncière de 1 200 € intégralement supportée par le locataire ; il dispose de deux extractions de 200 mm chacune ; une réserve supplémentaire de 36 m² peut être acquise pour 16 000 € ; l’actif est proposé à un prix net vendeur de 187 000 € ; 📞 Contact : Samuel Abbou – 07 82 55 86 75 Extraction possible.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), il reste environ 51 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 64 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
+++ b/docs/dossiers/dossier-st-denis-ae5e79a1.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
